--- a/scripts/qa-loop/artifacts/soroka/e2e/filled-soroka.xlsx
+++ b/scripts/qa-loop/artifacts/soroka/e2e/filled-soroka.xlsx
@@ -13,16 +13,152 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: תכנון וביצוע (תנאים מיוחדים, ע׳19). מקור אחר: ביצוע (מפרט טכני חדרי ניתוח צפוניים.pdf, ע׳1). מומלץ לאמת מול המקור. תנאים מיוחדים (תכנון וביצוע) מול מפרט טכני (ביצוע).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: תשלום התמורה יתבצע כמפורט בפרק 12 "חשבונות ותשלומים" בתנאים הכלליים. תנאי התשלום יהיו 45 יום ממועד קבלת החשבון כנדרש בכללית (סעיף 7.3 בתנאים המיוחדים). (תנאים מיוחדים, ע׳25). מקור אחר: תשלום חשבון חלקי מאושר תוך שוטף+93 יום לאחר מועד הגשת החשבון (סעיף 12.5) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳102). מומלץ לאמת מול המקור. 45 יום ממועד קבלת החשבון (תנאים מיוחדים) מול שוטף+93 יום (תנאים כלליים)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0">
+      <text>
+        <r>
+          <t>⚠ שדה מהותי (כסף/בטיחות) שלא נמצא לו מקור — יש לבדוק ידנית מול מסמכי המכרז.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: 500 (תנאים מיוחדים, ע׳27). מקור אחר: 2,000 (תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26.pdf, ע׳27). מומלץ לאמת מול המקור.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: הקבלן אחראי בלעדי לשמירה על הציוד, החומרים והמבנים. במקרה של קלקול, אבידה או גניבה ישא הקבלן בכל ההפסד; אין אחריות על המזמין (סעיף 00.05) (מפרט טכני חדרי ניתוח צפוניים, ע׳5). מקור אחר: הקבלן אחראי לשמירה 24 שעות ביממה כל ימות השנה על המבנה, העבודות והחומרים, מספק שומרים כשירים, סוגר ונועל חלקי מבנה עד מסירה (סעיף 3.5) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳25). מומלץ לאמת מול המקור. תנאים כלליים מול מפרט טכני ספציפי</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: הקבלן ינקה אתר הבניין מדי שבוע או תוך יומיים מקבלת הוראה, ובגמר העבודות; יפנה פסולת לאתר שפך מורשה (סעיף 00.32) (מפרט טכני חדרי ניתוח צפוניים, ע׳13). מקור אחר: הקבלן מנקה את האתר יום-יום, מסלק פסולת, חומרים שנפסלו ואשפה של כל הגורמים, ומבצע ניקוי סופי לפני קבלה מוקדמת (סעיף 6.11) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳55). מומלץ לאמת מול המקור. תנאים כלליים מול מפרט טכני ספציפי</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C53" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: הקבלן יתקין שלט באתר על חשבונו הכולל שם העבודה, שם המתכנן, שם הקבלן ופרטים נוספים; תוכן/גודל/מיקום נקבעים ע״י המפקח (סעיף 00.07) (מפרט טכני חדרי ניתוח צפוניים, ע׳5). מקור אחר: הקבלן מתקין שלט ראשי על גדר האתר הכולל שמות כללית והמתכננים, שלטי בטיחות והכוונה, ומעבירם לפי שלבי העבודה (סעיף 6.10א) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳55). מומלץ לאמת מול המקור. תנאים כלליים מול מפרט טכני ספציפי</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C55" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: לא תיעשה עבודת קבע בשעות הלילה, שבת, מועדי ישראל או ימי שבתון ללא היתר בכתב; נתיבי התנועה בשטח המזמין ייקבעו ע״י המפקח (סעיפים 00.13, 00.09) (מפרט טכני חדרי ניתוח צפוניים, ע׳6). מקור אחר: הקבלן עובד לפי חוק שעות עבודה ומנוחה, מקבל היתרים לעבודה בשבת/חג, אינו חוסם דרכים שלא לצורך ומקיים דרישות רשויות תנועה (סעיפים 9.4, 3.8.2) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳73). מומלץ לאמת מול המקור. תנאים כלליים מול מפרט טכני ספציפי</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C73" authorId="0">
+      <text>
+        <r>
+          <t>⚠ מקור ספציפי גובר על מקור כללי. נבחר: הקבלן הוא מבצע הבניה לפי תקנות הבטיחות; חובה למנות מנהל עבודה ולמסור הודעה; חובה למנות ממונה בטיחות; הגשת דו"ח בטיחות חודשי למהנדס; ליקויים יתוקנו; אי הגשת דו"ח מאפשר עיכוב תשלומים (סעיף 5.2) (תנאים מיוחדים, ע׳24). מקור אחר: הקבלן אחראי למילוי הוראות פקודת הבטיחות בעבודה, תקנות הבטיחות בעבודה (עבודות בניה) וכל דין אחר; חייב למנות ממונה בטיחות, לספק אמצעי בטיחות זמניים, להתקין גדרות ומעקות, להסדיר רשיונות כניסה ולפעול לפי נספחי בטיחות 3.1.3א(1)-(4) כולל הנחי</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C75" authorId="0">
+      <text>
+        <r>
+          <t>⚠ סתירה בין מקורות. נבחר: הקבלן אחראי לכל הבדיקות והאישורים הנדרשים לעמידה בתקני אש (ת״י 921, 1220, 1596 וכו׳), אינטגרציה, תקינות מערכות גילוי וכיבוי, תאורת חירום, דלתות אש, חשמל ותקרות מונמכות (סעיף 00.29) (מפרט טכני חדרי ניתוח צפוניים, ע׳12). מקור אחר: הקבלן מבצע בדיקות חומרים ועבודות במעבדה מוסמכת, נושא בהוצאות עד 0.5% משכר החוזה, ומבצע בדיקות חוזרות על חשבונו במקרה של כשל (סעיף 8.5) (תנאים כלליים פברואר 2022 - לוגו חדש.pdf, ע׳64). מומלץ לאמת מול המקור. תנאים כלליים מול מפרט טכני ספציפי</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="172">
-  <si>
-    <t>שיקום חדרי ניתוח צפוניים בבית חולים סורוקה (פרויקט 6733)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="163">
+  <si>
+    <t>שיקום חדרי ניתוח צפוניים בבית חולים סורוקה</t>
   </si>
   <si>
     <t>הוכן ע"י</t>
   </si>
   <si>
-    <t>מכרז</t>
+    <t>מסמך תנאי חוזה כלליים מהדורה מעודכנת לפברואר 2022, חלק בלתי נפרד מחוזה התקשרות עם קבלנים (עמוד 1)</t>
   </si>
   <si>
     <t>מספר</t>
@@ -46,19 +182,19 @@
     <t>אתר העבודות:</t>
   </si>
   <si>
-    <t>בבית חולים סורוקה</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 23</t>
+    <t>שיקום חדרי ניתוח צפוניים במ.ר סורוקה</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 1</t>
   </si>
   <si>
     <t>מזמין + מספר ח.פ:</t>
   </si>
   <si>
-    <t>שירותי בריאות כללית ח.פ. 5899026114</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 36</t>
+    <t>שירותי בריאות כללית ח.פ 5899026114</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 36</t>
   </si>
   <si>
     <t>מפקח:</t>
@@ -84,10 +220,10 @@
     </r>
   </si>
   <si>
-    <t>עבודות בינוי ומערכות אלקטרומכניות בשיקום חדרי ניתוח צפוניים בבית חולים סורוקה (פרויקט 6733)</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 1</t>
+    <t>תכנון וביצוע</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 19</t>
   </si>
   <si>
     <t>תנאי סף צוות ביצוע:</t>
@@ -96,7 +232,7 @@
     <t>מהנדס בניין רשום + מנהל עבודה רשום, כל אחד עם ניסיון מוכח של 5 שנים לפחות בעבודות דומות (סעיף 4.1)</t>
   </si>
   <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 24</t>
+    <t>תנאים מיוחדים — עמוד 24</t>
   </si>
   <si>
     <r>
@@ -124,16 +260,16 @@
     </r>
   </si>
   <si>
-    <t>פנייה לקבלת הצעות מחיר; בחירה בהצעה הזולה ביותר; תוקף הצעות עד 180 יום מהמועד האחרון להגשה</t>
+    <t>פנייה לקבלת הצעות מחיר; הכללית תבחר בהצעה הזולה ביותר (סעיף 4)</t>
   </si>
   <si>
     <t>האם יש הליך תחרותי נוסף? ככל וכן - תנאים:</t>
   </si>
   <si>
-    <t>כן — המזמינה רשאית לפנות למציע השני במדרג תוך 10 ימים מהודעה; אם לא יענה — רשאית לפנות לשלישי וכן הלאה (סעיף 23)</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 4</t>
+    <t>המזמינה רשאית לפנות למציע השני (ואילך) אם הזוכה אינו עומד בהתחייבויותיו; למציע השני 10 ימים להודיע (סעיף 23)</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 3</t>
   </si>
   <si>
     <t>בתכנון ביצוע- מי הגורם מטעמו מגיע האדריכל ויועץ הבטיחות</t>
@@ -154,49 +290,43 @@
     <t>אבני דרך חוזיות:</t>
   </si>
   <si>
-    <t>משך הביצוע הוא עד 7 חודשים קלנדריים מיום קבלת אישור המזמין להתחלת העבודות (כולל מסירה והפעלה); הזוכה חייב להתחיל ביצוע תוך 7 ימים מקבלת הודעת הזכייה; ערבות ביצוע תימסר תוך 7 ימים מקבלת הודעת קבלת ההצעה (סעיף 17, סעיף 3 בתנאים המיוחדים, סעיף 5 בהזמנה).</t>
+    <t>לוח הזמנים המפורט כולל את כל המועדים ושלבי הביניים הקריטיים (סעיף 9.3.1). הקבלן חייב לעמוד בלוח הזמנים ובכל חלק ממנו; איחור בשלבי ביניים קריטיים מזכה בפיצויים מוסכמים של 0.5% משכר החוזה לכל שבוע או חלק ממנו (סעיף 9.5.1.2).</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 70</t>
   </si>
   <si>
     <t>סכום החוזה:</t>
   </si>
   <si>
-    <t>יש לקרוא סעיף 12.4 (עמוד 101)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 101</t>
-  </si>
-  <si>
     <t>+ מדידה/פאושלי</t>
   </si>
   <si>
-    <t>מדידה — המציע ממלא מחירי יחידה בכתב הכמויות; כללית בוחרת בהצעה הזולה ביותר (סעיף 4)</t>
-  </si>
-  <si>
     <t>כקבלן משנה - מה מקבלים/ ומה הקיזוז/עד מתי:</t>
   </si>
   <si>
-    <t>עמלת שירותים 3% (או 12% בהתקשרות ישירה) מחשבונות חלקיים/סופיים של קבלנים אחרים (ללא מע"מ, ללא מקדמות, ללא ציוד/מכונות); עבודות כלולות: חשמל/תקשורת (ללא לוחות/גופי תאורה), אינסטלציה (ללא דודים/משאבות), מיזוג אוויר (ללא יחידות קירור), בקרה, מעליות (ללא מחיר המעלית), גנרטור, אלומיניום, תקרות אקוסטיות, חיפויים, צבע, נגרות, מתח גבוה, מחיצות גבס, מסגרות, עבודות אבן (סעיף 4.2.8)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 38</t>
+    <t>הקבלן רשאי להעסיק קבלני משנה רשומים רק באישור מראש ובכתב מכללית/המהנדס; אין שחרור מאחריות; המהנדס רשאי להרחיק קבלן משנה (סעיף 4.3)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 40</t>
   </si>
   <si>
     <t>תוכניות:</t>
   </si>
   <si>
-    <t>הקבלן נדרש לחתום על כל התוכניות (נספח ז׳) תוך 7 ימים מקבלת הודעת זכייה; חתימה על תצהיר נספח ד׳ מהווה תחליף חתימה</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 3</t>
+    <t>רשימת תוכניות אדריכלות, קונסטרוקציה, אינסטלציה, חשמל, מיזוג אויר, בטיחות</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 255</t>
   </si>
   <si>
     <t>יומנים:</t>
   </si>
   <si>
-    <t>הקבלן מחויב להגיש יומני עבודה באמצעות מערכת רמדורנט; כל דיווח תקף רק אם הוגש דרך המערכת</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 26</t>
+    <t>המהנדס מנהל יומן עבודה יומי ב-4 עותקים הכולל מספר עובדים, כמויות חומרים, ציוד, תנאי מזג אוויר, תקלות, הוראות והתקדמות; הקבלן רשאי להעיר תוך 3 ימים והרישומים משמשים ראיה (סעיף 6.5)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 49</t>
   </si>
   <si>
     <t xml:space="preserve">עמלות נוספות: </t>
@@ -205,22 +335,25 @@
     <t>הצמדה:</t>
   </si>
   <si>
-    <t>הצמדה למדד מחירי התשומה בבניה למגורים — ערבויות ותשלומים צמודים למדד זה; אין התייקרויות אחרות (סעיף 12.2.8 בתנאים הכלליים)</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 6</t>
+    <t>התייקרויות לפי תנודות במדד מחירי התשומה בבניה למגורים/שע"ח בין מדד הבסיס לבין המדד/שע"ח שיהיה ידוע ביום הגבייה בפועל (סעיף 12.2, 9.5.7)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 74</t>
   </si>
   <si>
     <t>מדד הבסיס:</t>
   </si>
   <si>
-    <t>יש לקרוא סעיף 12.2 (עמוד 96)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 96</t>
+    <t>המדד/שע"ח הקבוע בסעיף3לחוזה-מסמך4 (סעיף 12.2.1)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 96</t>
   </si>
   <si>
     <t>המדד הקובע/החדש:</t>
+  </si>
+  <si>
+    <t>המדד/שע"ח הממוצע של החודש בו הסתיימה התקופה הקובעת (סעיף 12.2.1)</t>
   </si>
   <si>
     <t>עיכבון:</t>
@@ -230,10 +363,10 @@
 השתתפות /ע"י הקבלן:</t>
   </si>
   <si>
-    <t>הקבלן משלם לכללית 0.525% מסך כל מחיר העבודות (כולל מע"מ) כחלקו בפרמיות ביטוח עבודות קבלניות (סעיף 6).</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 25</t>
+    <t>הקבלן חייב בביטוח חבות מעבידים (לכל תקופת הביצוע + תחזוקה), חבות מוצר (3 שנים לפחות), אחריות מקצועית (5 שנים לאחר מסירה, לפרויקטים מעל 5 מיליון ₪); כללית מבוטחת נוספת (סעיף 3.10.9)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 29</t>
   </si>
   <si>
     <r>
@@ -262,43 +395,34 @@
     </r>
   </si>
   <si>
-    <t>הקבלן חייב לערוך ביטוח חבות מעבידים (20 מיליון ₪), חבות מוצר (4 מיליון ₪, 3 שנים), אחריות מקצועית (4 מיליון ₪, 3 שנים) + ביטוחי רכב, ציוד, אש מורחב; הפוליסות ראשוניות, ויתור על שיבוב, ללא חריג רשלנות רבתי (נספח ג' עמוד 33-36).</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 33</t>
+    <t>הקבלן חייב בביטוח עבודות קבלניות (פוליסה של כללית) + ביטוחים משלימים לפי אישור קיום ביטוחים; חובה להמציא אישורים לפני תחילה ובסיום; כללית רשאית לדרוש אישור נוסף מהמשכיר/בעל הקרקע (סעיף 3.10.9–3.10.11)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 30</t>
   </si>
   <si>
     <t>קיזוזים חוזיים נוספים:</t>
   </si>
   <si>
-    <t>כללית תהיה רשאית לקזז מכל סכום שיגיע לקבלן מכללית, בין על פי חוזה זה ובין מכל סיבה אחרת, כל סכום המגיע או שיגיע מהקבלן לכללית, בתוספת ריבית חוקית והפרשי התייקרות (סעיף 14.1).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 108</t>
-  </si>
-  <si>
     <t>מקדמה:</t>
   </si>
   <si>
-    <t>יש לקרוא סעיף 8.2.5 (עמוד 61)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 61</t>
-  </si>
-  <si>
     <t>תנאי תשלום חשבונות ביניים:</t>
   </si>
   <si>
-    <t>תנאי התשלום יהיו 45 יום ממועד קבלת החשבון כנדרש בכללית (סעיף 7.3).</t>
+    <t>תשלום התמורה יתבצע כמפורט בפרק 12 "חשבונות ותשלומים" בתנאים הכלליים. תנאי התשלום יהיו 45 יום ממועד קבלת החשבון כנדרש בכללית (סעיף 7.3 בתנאים המיוחדים).</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 25</t>
   </si>
   <si>
     <t>אופן הגשת חשבון ביניים:</t>
   </si>
   <si>
-    <t>בתחילת כל חודש קלנדרי ימציא הקבלן למהנדס חשבון חלקי בגין החודש הקודם הכולל: דפי ריכוז כמויות, חשבון מצטבר מוקלד בתוכנת כתב הכמויות, חשבון התייקרויות, העתק יומני עבודה, רשימות עבודות יומיות, הוראות שינויים, אישורי מינהל תשתיות ובינוי (סעיף 12.1.1). החשבון יוגש ב-3 עותקים + דיסקט/תקליטור.</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 92</t>
+    <t>הקבלן מגיש בתחילת כל חודש חשבון חלקי מצטבר מוקלד בתוכנת כתב הכמויות + דפי ריכוז + חשבון התייקרויות + יומנים + אישורים; המהנדס בודק תוך 14 יום ומאשר (סעיף 12.1)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 91</t>
   </si>
   <si>
     <t>גורם מאשר חשבון:</t>
@@ -307,10 +431,10 @@
     <t>תנאי תשלום חשבון סופי:</t>
   </si>
   <si>
-    <t>התשלום על פי החשבון הסופי כפי שיאושר לתשלום יבוצע תוך שוטף+93 יום לאחר מועד הגשת החשבון הסופי או תוך 30 יום מיום אישורו לתשלום על ידי המהנדס, לפי המאוחר (סעיף 12.5). התשלום יבוצע באמצעות שיק או העברת כספים ישירות לחשבון הבנק בכפוף למילוי נספח "12.5".</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 102</t>
+    <t>תשלום חשבון סופי מאושר תוך שוטף+93 יום לאחר מועד הגשת החשבון או תוך30 יום מיום אישורו, לפי המאוחר (סעיף 12.5)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 102</t>
   </si>
   <si>
     <t>ערבות הצעה:</t>
@@ -319,118 +443,112 @@
     <t>ערבות ביצוע:</t>
   </si>
   <si>
-    <t>ערבות בנקאית לביצוע כל ההתחייבויות על פי החוזה, צמודה למדד, על סך 5% מסך כל מחיר העבודות כמופיע בכתב הכמויות + מע"מ, בנוסח המצורף לתנאים המיוחדים (סעיף 15.1.1). כללית רשאית להפחית את הסכום לפי שיקול דעתה הבלעדי בכפוף לאישור ראש מינהל תשתיות ובינוי ומנהל/ת הכספים.</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 110</t>
+    <t>ערבות ביצוע בנוסח נספח א1; ערוכה לטובת המזמין + משרד הבריאות; תוקף עד מועד שייקבע (סעיף 9.1)</t>
   </si>
   <si>
     <t>ערבות בדק:</t>
   </si>
   <si>
-    <t>ערבות בנקאית צמודה למדד לבדק: 5% מהסכום הכולל הנדרש בחשבון הסופי (למעט איטום) + מע"מ לתקופה של 24 חודשים; 10% מהסכום לעבודות איטום + מע"מ לתקופה של 5 שנים, בנוסח המצורף (סעיף 15.1.3). תוקף הערבות עד תום תקופת האחריות הרלוונטית.</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 111</t>
+    <t>ערבות בדק 24 חודשים ממועד מסירה (נספח א2) + ערבות בדק איטום (נספח א3) (סעיף 9.1)</t>
   </si>
   <si>
     <t xml:space="preserve">תקופות הבדק: </t>
   </si>
   <si>
-    <t>בדק כללי 24 חודשים; מערכות מכניות 24 חודשים; מכונות ומנועים 36 חודשים; אספלט ופיתוח 36 חודשים; איטום 60 חודשים; חיפויים חיצוניים 84 חודשים (סעיף 13.5)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 106</t>
+    <t>24 חודשים ממועד מסירת הפרויקט למזמין (ערבות בדק)</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 28</t>
   </si>
   <si>
     <t>תקופת אחריות:</t>
   </si>
   <si>
-    <t>24 חודשים ממועד מסירת הפרויקט למזמין</t>
-  </si>
-  <si>
-    <t>תנאים מיוחדים- ביח בחירום-סורוקה - שיקום חדרי ניתוח צפוניים מעודכן 27.1.26 — עמוד 27</t>
+    <t>24 חודשים</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 26</t>
   </si>
   <si>
     <t>הוראות שינויים, סמכות מאשרת:</t>
   </si>
   <si>
-    <t>הוראת שינויים ניתנת בכתב ע"י ראש מינהל תשתיות ובינוי או נציגו או המהנדס; הקבלן חייב לבצע מיידית גם אם טרם נקבע ערך; הוראה החורגת מ-10% משכר החוזה או 100,000 ₪ דורשת הזמנת עבודה חתומה מראש (סעיף 10.3.2.1, 10.3.2.5).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 83</t>
+    <t>המהנדס או ראש מינהל תשתיות ובינוי רשאי להורות בכתב על שינויים בכל שלב; הוראת שינויים חורגת (תוספת 10% או 100,000 ₪) מחייבת הזמנת עבודה חתומה מראש (סעיף 10.3.2).</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 83</t>
   </si>
   <si>
     <t>קביעת מחיר השינויים:</t>
   </si>
   <si>
-    <t>יש לקרוא סעיף 11.3 (עמוד 88)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 88</t>
+    <t>מחיר יחידה נוסף ייקבע על ידי המהנדס לאחר דיון עם הקבלן לפי ניתוח מחירים (השוואה למחירי יחידה בכתב הכמויות או ממקורות אחרים) או ניתוח עלויות (עלויות משוערות +12%) (סעיף 11.3)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 88</t>
   </si>
   <si>
     <t>הגדלה והקטנה של היקף העבודה:</t>
   </si>
   <si>
-    <t>הקטנת היקף העבודות אינה מזכה את הקבלן בפיצוי כלשהו; הגדלה מחייבת הוראת שינויים בכתב וקביעת ערך לפי מחירי יחידה קיימים או מחירי יחידה נוספים (סעיף 10.3.3.3, 10.3.3.1).</t>
-  </si>
-  <si>
     <t>הגדרת תכולת עבודה בפאושל:</t>
   </si>
   <si>
+    <t>כל האמור במפרט הכללי, בתנאים הכלליים המיוחדים, במפרט המיוחד ובתוכניות, לרבות כל פרט ו/או הוראה המצויינים במסמכים הנ"ל ובשאר מסמכי החוזה ושלא נמדדו בסעיף נפרד בכתב הכמויות, כלול בהצעת הקבלן באופן כללי ובמחירי היחידה שבכתב הכמויות</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 16</t>
+  </si>
+  <si>
     <t>הארכת משך ביצוע:</t>
   </si>
   <si>
-    <t>הקבלן רשאי להגיש בקשה לדחייה עקב כח עליון, עיכובים או חוסר תוכניות; אורך הארכה נקבע ע"י ראש מינהל תשתיות ובינוי; אין זכות להוצאות אתר/תקורה (סעיף 9.7)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 76</t>
+    <t>הקבלן רשאי לבקש דחייה עקב כח עליון, עיכובים שלא בשליטתו או חוסר תוכניות (סעיף 9.7.1). הבקשה תוגש עד ה-5 בכל חודש; אורך הארכה נקבע ע"י ראש מינהל תשתיות ובינוי וקביעתו סופית (סעיף 9.7.3). אין זכות להוצאות אתר/תקורה בגין הארכה (סעיף 9.7.5).</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 76</t>
   </si>
   <si>
     <t>פיצוי בגין איחור:</t>
   </si>
   <si>
-    <t>פיצויים מוסכמים בסך 0.5% משכר החוזה לכל שבוע או חלק משבוע של איחור בהשלמת העבודות או שלב ביניים קריטי; ניתן לקיזוז או חילוט ערבות (סעיף 9.5.1.1, 9.5.1.2, 9.5.6).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 73</t>
+    <t>תנאים מיוחדים — עמוד 27</t>
   </si>
   <si>
     <t>פיצויים מוסכמים נוספים:</t>
   </si>
   <si>
-    <t>בכל מקרה של אי ציות להוראה מאת המהנדס/המפקח הנוגרת לפינוי מכולה מלאה, ישלם הקבלן לכללית פיצויים מוסכמים בסך 2,000 ש״ח לכל יום איחור (סעיף 10.2). במקרה של הטלת קנס על יותר מעילה אחת יחולו ההוראות במצטבר (סעיף 10.3). הקנסות ינקטו כמוצא אחרון ולאחר מתן התראה (סעיף 10).</t>
+    <t>500 per day for site cleanliness violations; 2000 per day for failure to empty full container</t>
   </si>
   <si>
     <t xml:space="preserve">שמירה: </t>
   </si>
   <si>
-    <t>הקבלן אחראי לשמירה 24 שעות ביממה כל ימות השנה על מקום המבנה, העבודות והחומרים; יספק שומרים כשירים, נשק, מבנה ושירותים; אחראי גם על עבודות קבלנים אחרים (סעיף 3.5.1).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 25</t>
+    <t>הקבלן אחראי בלעדי לשמירה על הציוד, החומרים והמבנים. במקרה של קלקול, אבידה או גניבה ישא הקבלן בכל ההפסד; אין אחריות על המזמין (סעיף 00.05)</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 5</t>
   </si>
   <si>
     <t>ניקיון:</t>
   </si>
   <si>
-    <t>בכל מקרה של אי ציות להוראות מאת המהנדס/המפקח הנוגעת לניקיון הכללי של אתר העבודה, ישלם הקבלן לכללית פיצויים מוסכמים בסך 500 ש״ח לכל יום איחור (סעיף 10.1). הקנסות ינקטו כמוצא אחרון ולאחר מתן התראה לתיקון הנדרש (סעיף 10).</t>
+    <t>הקבלן ינקה אתר הבניין מדי שבוע או תוך יומיים מקבלת הוראה, ובגמר העבודות; יפנה פסולת לאתר שפך מורשה (סעיף 00.32)</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 13</t>
   </si>
   <si>
     <t>שילוט:</t>
   </si>
   <si>
-    <t>הקבלן מתקין שלט ראשי על גדר האתר הכולל שמות כללית והמתכננים; שלטי בטיחות, הכוונה והתמצאות; כל שילוט נוסף דורש אישור מוקדם של המהנדס (סעיף 6.10.1א, 6.10.2א).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 55</t>
+    <t>הקבלן יתקין שלט באתר על חשבונו הכולל שם העבודה, שם המתכנן, שם הקבלן ופרטים נוספים; תוכן/גודל/מיקום נקבעים ע״י המפקח (סעיף 00.07)</t>
   </si>
   <si>
     <t>משרדי מפקח:</t>
   </si>
   <si>
-    <t>על הקבלן להקים תוך 7 ימים מבנה 35 מ"ר מחולק לשני חדרים כמשרד למפקח, כולל דלת, חלונות, ארונות, שולחנות, כסאות, מכונת צילום, מחשב, מדפסת, מזגן, לוח תכניות, אייפד וכל הציוד; מחיר ההקמה והאחזקה כלול במחירי היחידה (סעיף 00.22).</t>
+    <t>לא יאוחר מ-7 ימים מיום צו התחלת עבודה יקים הקבלן משרד למפקח בשטח 35 מ״ר מחולק לשני חדרים, כולל דלת, חלונות, ארונות, שולחנות, כסאות, מכונת צילום, מחשב, מדפסת, מזגן, מסך 75״ ואייפד (סעיף 00.22)</t>
   </si>
   <si>
     <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 9</t>
@@ -439,40 +557,37 @@
     <t>שעות עבודה והסדרי תנועה:</t>
   </si>
   <si>
-    <t>עבודה בשעות מנוחה, שבת ומועדים אסורה אלא בהיתר; הקבלן אחראי להסדרי תנועה, שילוט, תמרור ומניעת חסימה מיותרת של דרכים; חייב ברישיונות ובתיאום עם רשויות (סעיף 9.4.2, 3.8.2.1, 3.8.5.1).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 72</t>
+    <t>לא תיעשה עבודת קבע בשעות הלילה, שבת, מועדי ישראל או ימי שבתון ללא היתר בכתב; נתיבי התנועה בשטח המזמין ייקבעו ע״י המפקח (סעיפים 00.13, 00.09)</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 6</t>
   </si>
   <si>
     <t>מים וחשמל:</t>
   </si>
   <si>
-    <t>הקבלן אחראי לחיבור מים וחשמל זמני, על חשבונו, כולל מונה, אגרות, צריכה, תאורה זמנית וטלפון; יפרק בסיום (סעיפים 6.9, 6.10)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 54</t>
+    <t>המזמין ירשה לקבלן להשתמש בחשמל ומים לצורך ביצוע העבודה ולהתחבר לצורך כך לרשתות הקיימות של החשמל והמים במקום, אולם הדבר ייעשה לפי התנאים הבאים: א. ההתחברויות תעשינה במקומות שיקבעו על ידי המפקח ולפי התנאים שיקבעו על ידו כולל מונים מתאימים. ב. כל ההוצאות עבור השימוש השוטף במים וחשמל וכן של התקנת ההתחברויות ושל הסרתן בתום ביצוע העבודה והחזרת המצב לקדמותו, תחולנה על הקבלן בלבד. ג. המזמין לא יהיה אחראי עבור הספקה בלתי מספקת או בלתי סדירה, הפסקות או תקלות באספקת המים והחשמל. על הקבלן לעשות מראש, על חשב</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 4</t>
   </si>
   <si>
     <t>מעליות/עגורנים/במות הרמה:</t>
   </si>
   <si>
-    <t>הקבלן מתקין ומתחזק מעליות, עגורנים, פיגומים, במות וציוד הרמה זמני לכל המפלסים; אחראי ליציבות ובטיחות (סעיף 6.8)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 53</t>
+    <t>הקבלן מתקין ומתחזק מעליות, עגורנים, פיגומים, במות ומערכות תימוך לכל המפלסים, מאפשר שימוש לקבלנים אחרים ומפרק בסיום (סעיפים 6.8.3-6.8.5)</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 53</t>
   </si>
   <si>
     <t xml:space="preserve">קנסות: </t>
   </si>
   <si>
-    <t>בכל מקרה של אי ציות להוראות המהנדס/המפקח בנוגע לניקיון אתר העבודה – 500 ₪ ליום איחור; אי פינוי מכולה מלאה – 2,000 ₪ ליום איחור. הקנסות יוטלו כמוצא אחרון לאחר התראה, ויחולו במצטבר במקרה של הפרות מרובות (סעיף 10).</t>
-  </si>
-  <si>
     <t>האם קיים היתר?+היתר שינויים מתאים:</t>
   </si>
   <si>
-    <t>הקבלן אחראי לקבלת תעודת גמר לפרויקט ובין היתר: טופס 4, טופס 5, אישור אכלוס משרותי הכבאות, אישור פיקוד העורף, אישור מעבדת תקינה לאינטגרציה בין המערכות וכל אישור אחר שיידרש לאכלוס הבנין (סעיף 00.41).</t>
+    <t>כן — הקבלן אחראי לקבלת תעודת גמר לפרויקט ובין היתר: טופס4, טופס5, אישור אכלוס משרותי הכבאות, אישור פיקוח העורף, אישור מעבדת תקינה לאינטגרציה בין המערכות וכל אישור אחר שיידרש לאכלוס הבנין (סעיף 00.41)</t>
   </si>
   <si>
     <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 15</t>
@@ -484,16 +599,13 @@
     <t>טופס 4 ותעודת גמר מהרשות:</t>
   </si>
   <si>
-    <t>הקבלן אחראי לקבלת תעודת גמר לפרויקט ובין היתר: טופס 4, טופס 5, אישור אכלוס משרותי הכבאות, אישור פיקוד העורף, אישור מעבדת תקינה לאינטגרציה בין המערכות וכל אישור אחר שיידרש לאכלוס הבנין (סעיף 00.41); הגשת כל התעודות הנ"ל הינה תנאי לתשלום חשבון סופי (סעיף 00.29).</t>
+    <t>כן — הקבלן אחראי לקבלת תעודת גמר לפרויקט ובין היתר: טופס4, טופס5, אישור אכלוס משרותי הכבאות, אישור פיקוד העורף, אישור מעבדת תקינה לאינטגרציה בין המערכות וכל אישור אחר שיידרש לאכלוס הבנין (סעיף 00.41)</t>
   </si>
   <si>
     <t>הפסקות עבודה והפיצוי בגינן:</t>
   </si>
   <si>
-    <t>הפסקה זמנית לפי הוראת כללית: הוצאות ישירות על כללית (אם הודעה תוך 30 יום); אין פיצוי אם באשמת הקבלן או תנאי מזג אוויר (סעיף 9.8)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 77</t>
+    <t>לא — אין פיצוי כספי על הפסקות עבודה; המפקח רשאי להפסיק עבודה ללא עילה לתביעה כספית (סעיף 00.15 ד); עיכובים עקב מזג אוויר אינם כוח עליון (סעיף 00.16); אין פיצוי על תגבור או עבודה בשעות נוספות (סעיף 00.21)</t>
   </si>
   <si>
     <t>הגבלה בדבר שינוי שליטה:</t>
@@ -502,91 +614,88 @@
     <t>ויתור על זכות העיכבון:</t>
   </si>
   <si>
-    <t>לקבלן אין זכות עיכבון על המקרקעין, העבודות, החומרים או כספים (סעיף 14.5)</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 109</t>
+    <t>לקבלן אין זכות עיכבון מכל סוג על המקרקעין, העבודות, החומרים, הציוד או כספים של כללית (סעיף 14.5).</t>
+  </si>
+  <si>
+    <t>תנאים כלליים פברואר 2022 — עמוד 109</t>
   </si>
   <si>
     <t>שעבוד/העברת הסכם:</t>
   </si>
   <si>
-    <t>הקבלן אינו רשאי להמחות זכויותיו (לרבות כספים) לצד ג' ללא הסכמה בכתב מראש של כללית; הסכמה כפופה לתנאים שייקבעו לפי שיקול דעתה הבלעדי (סעיף 11).</t>
+    <t>הקבלן אינו רשאי להמחות זכויותיו (לרבות הזכות לקבלת כספים) על פי ההסכם לצד ג' כלשהו ללא הסכמת כללית מראש ובכתב; הסכמה כפופה לתנאים שייקבעו על ידי כללית (סעיף 11)</t>
   </si>
   <si>
     <t>פתרון סכסוכים:</t>
   </si>
   <si>
-    <t>סמכות ייחודית לבית המשפט המוסמך בתל אביב-יפו לכל עניין הנוגע להליך או הנובע ממנו; המציעים מוותרים מראש על זכות לפנות לבית משפט אחר (סעיף 24)</t>
+    <t>סמכות מקומית ייחודית ובלעדית לבית המשפט המוסמך בתל אביב-יפו לכל עניין הנוגע להליך (סעיף 24).</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 4</t>
   </si>
   <si>
     <t>סעיף בוררות - האם קיים?</t>
   </si>
   <si>
-    <t>לא — אין סעיף בוררות; הסמכות הבלעדית נתונה לבית המשפט בתל אביב-יפו (סעיף 24)</t>
+    <t>לא — הסמכות המקומית הייחודית והבלעדית נתונה לבית המשפט המוסמך בתל אביב-יפו; אין סעיף בוררות (סעיף 24)</t>
   </si>
   <si>
     <t>סדר עדיפות במסמכים ו/או מקרים של סתירה במסמכים:</t>
   </si>
   <si>
-    <t>במקרה של סתירה בין התנאים הכלליים לתנאים המיוחדים — יגבר האמור בתנאים המיוחדים (סעיף 1.2)</t>
+    <t>במקרה של סתירה בין התנאים הכלליים לתנאים המיוחדים — יגברו התנאים המיוחדים (סעיף 1.2).</t>
+  </si>
+  <si>
+    <t>תנאים מיוחדים — עמוד 23</t>
   </si>
   <si>
     <t>הגבלה על העסקת עובדים:</t>
   </si>
   <si>
-    <t>הקבלן מתחייב להעסיק במשך כל תקופת הביצוע מנהל עבודה מוסמך, מקצועי, מנוסה, ומומחה לעבודות המתוארות במפרט זה. לא יאושר לבצע כל סוג שהוא של עבודה ללא נוכחות רצופה של מנהל העבודה מטעם הקבלן (סעיף 00.23).</t>
-  </si>
-  <si>
-    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 10</t>
-  </si>
-  <si>
     <t>תנאי סף לקבלני משנה:</t>
   </si>
   <si>
-    <t>קבלן משנה חייב להיות רשום ורשוי; נדרש אישור מראש ובכתב מכללית/המהנדס לאחר הגשת בקשה מפורטת; חלק מקבלני המשנה ייבחרו מרשימה שתקבע כללית בתנאים המיוחדים; אסור להחליף ללא אישור מוקדם (סעיפים 4.3.1–4.3.2).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 40</t>
+    <t>קבלן משנה חייב להיות קבלן רשום ורשוי לפי חוק רישום הקבלנים, לקבל אישור מראש ובכתב מכללית ו/או המהנדס לאחר הגשת בקשה בכתב המפרטת כישורים; חלק מקבלני המשנה ייבחרו מרשימה שתקבע כללית (סעיף 4.3.1).</t>
   </si>
   <si>
     <t>פרקים בהם יש קבלנים מוכתבים:</t>
   </si>
   <si>
-    <t>סעיף 5.1 — קבלנים אחרים כוללים: שלד וגמר, אינסטלציה, חשמל, נגרות, מסגרות, אלומיניום, ציוד רפואי, גילוי אש, בקרה, מיזוג אוויר (סעיף 5.1)</t>
+    <t>קבלן שלד ועבודות גמר; קבלן אינסטלציה; קבלן חשמל; קבלני נגרות; קבלני מסגרות; קבלן אלומיניום; קבלני ציוד רפואי; קבלן גילוי אש; קבלן בקרה; קבלן מיזוג אויר</t>
   </si>
   <si>
     <t>התקשרויות עם קבלנים אחרים וממונים:</t>
   </si>
   <si>
-    <t>הקבלן אחראי להתקשרויות עם קבלנים אחרים; כללית רשאית להוסיף קבלנים נוספים מעת לעת; הקבלן נושא באחריות מלאה לפעולותיהם (סעיף 5.1)</t>
+    <t>הקבלן מתקשר עם קבלנים אחרים (שלד, אינסטלציה, חשמל, נגרות, מסגרות, אלומיניום, ציוד רפואי, גילוי אש, בקרה, מיזוג) כמפורט; כללית רשאית להוסיף קבלנים נוספים לפי שיקול דעתה</t>
   </si>
   <si>
     <t xml:space="preserve">הוראות/הערות בטיחות: </t>
   </si>
   <si>
-    <t>הקבלן הוא ״מבצע הבניה״ לפי תקנות הבטיחות; חובה למנות מנהל עבודה וממונה בטיחות; הגשת דו״ח בטיחות חודשי; כללית רשאית לעכב תשלומים בגין אי הגשה או אי תיקון ליקויים (סעיף 5.2)</t>
+    <t>הקבלן הוא מבצע הבניה לפי תקנות הבטיחות; חובה למנות מנהל עבודה ולמסור הודעה; חובה למנות ממונה בטיחות; הגשת דו"ח בטיחות חודשי למהנדס; ליקויים יתוקנו; אי הגשת דו"ח מאפשר עיכוב תשלומים (סעיף 5.2)</t>
   </si>
   <si>
     <t>מסירת העבודה ותעודת השלמה:</t>
   </si>
   <si>
-    <t>הקבלן מודיע על סיום; המהנדס מכנס ועדת קבלה מוקדמת/סופית; נדרש ניקוי סופי, תכניות עדות, אישורים מרשויות ותעודת גמר אחריות; תקופת אחריות מתחילה ממועד המסירה הסופית (סעיפים 13.1.1–13.7).</t>
-  </si>
-  <si>
-    <t>תנאים כלליים פברואר 2022 - לוגו חדש — עמוד 103</t>
+    <t>משך הביצוע כולל מסירה והפעלה של המבנה; הקבלן אחראי לכל אישור נדרש על פי דין ובדיקות מעבדה לצורך אכלוס (סעיף 3)</t>
   </si>
   <si>
     <t>בדיקות:</t>
   </si>
   <si>
-    <t>הקבלן אחראי לכל אישור הנדרש על פי הדין וכן בדיקות מעבנה לצורך אכלוס המבנה (סעיף 3)</t>
+    <t>הקבלן אחראי לכל הבדיקות והאישורים הנדרשים לעמידה בתקני אש (ת״י 921, 1220, 1596 וכו׳), אינטגרציה, תקינות מערכות גילוי וכיבוי, תאורת חירום, דלתות אש, חשמל ותקרות מונמכות (סעיף 00.29)</t>
+  </si>
+  <si>
+    <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 12</t>
   </si>
   <si>
     <t>בקרת איכות:</t>
   </si>
   <si>
-    <t>הקבלן חייב לבצע בקרת איכות בכל שלבי הביצוע. בקר איכות יהיה חשמלאי רשוי (מוסמך לפחות) עם ניסיון מוכח באתרים רפואיים קבוצה 2. כל שלב ביצוע יתועד וייבדק ע"י בקרת איכות חשמל או בודק מוסמך; לא יאושר להתקדם לפני קבלת דוח. כל הדוחות והתיעוד כלולים במחיר העבודה ולא ישולם בנפרד (סעיף 7).</t>
+    <t>בקרת איכות חובה בכל שלבי הביצוע; בקר איכות חשמל חייב להיות חשמלאי רשוי עם ניסיון מוכח באתרים רפואיים קבוצה 2; כל שלב יתועד וייבדק; כל הדוחות כלולים במחיר העבודה (סעיפים 7.1-7.6)</t>
   </si>
   <si>
     <t>מפרט טכני חדרי ניתוח צפוניים — עמוד 54</t>
@@ -674,12 +783,22 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE9A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -751,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,6 +886,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -792,12 +914,14 @@
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1243,965 +1367,945 @@
       <c r="B4" s="6">
         <v>44593</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" ht="38.45" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="12"/>
     </row>
     <row r="7" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>1</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="15"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>6</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>8</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>9</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>10</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>11</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>12</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>13</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>14</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>15</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>16</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="16"/>
+    </row>
+    <row r="23" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>17</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>18</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>9</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="B25" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>20</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="16"/>
+    </row>
+    <row r="27" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>21</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>22</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>23</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
+        <v>24</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="16"/>
+    </row>
+    <row r="31" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
         <v>25</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="B31" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
         <v>26</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="B32" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>10</v>
-      </c>
-      <c r="B16" s="17" t="s">
+      <c r="B33" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="16"/>
+    </row>
+    <row r="34" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="13">
         <v>28</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-    </row>
-    <row r="17" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>11</v>
-      </c>
-      <c r="B17" s="17" t="s">
+      <c r="B34" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="16"/>
+    </row>
+    <row r="35" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="13">
         <v>29</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-    </row>
-    <row r="18" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>12</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="B35" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
         <v>30</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-    </row>
-    <row r="19" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>13</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
         <v>31</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="B37" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+    </row>
+    <row r="38" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="13">
         <v>32</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>14</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
         <v>33</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="B39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="16"/>
+    </row>
+    <row r="40" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="13">
         <v>34</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>15</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="B40" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
         <v>35</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="B41" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
         <v>36</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="B42" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="13">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>16</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="B43" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="13">
         <v>38</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="B44" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
         <v>39</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>17</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="B45" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
         <v>40</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="B46" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
         <v>41</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="B47" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
         <v>42</v>
       </c>
-    </row>
-    <row r="24" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
-        <v>18</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="B48" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
         <v>43</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="B49" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="17">
+        <v>500</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="13">
         <v>44</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="B50" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>19</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="B51" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="13">
         <v>46</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="B52" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="13">
         <v>47</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="B53" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="13">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>20</v>
-      </c>
-      <c r="B26" s="13" t="s">
+      <c r="B54" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="13">
         <v>49</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-    </row>
-    <row r="27" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>21</v>
-      </c>
-      <c r="B27" s="13" t="s">
+      <c r="B55" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="13">
         <v>50</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="B56" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="13">
         <v>51</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="B57" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="13">
         <v>52</v>
       </c>
-    </row>
-    <row r="28" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="B58" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="13">
+        <v>53</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="13">
+        <v>54</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+    </row>
+    <row r="61" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="13">
+        <v>55</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="13">
+        <v>56</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="13">
+        <v>57</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+    </row>
+    <row r="64" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="13">
+        <v>58</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="13">
+        <v>59</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="13">
+        <v>60</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="13">
+        <v>61</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="13">
+        <v>62</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="13">
+        <v>63</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+    </row>
+    <row r="70" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="13">
+        <v>64</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="13">
+        <v>65</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>23</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
-        <v>24</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
-        <v>25</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
-        <v>26</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
-        <v>27</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="15" t="s">
+    </row>
+    <row r="72" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="13">
         <v>66</v>
       </c>
-    </row>
-    <row r="34" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
-        <v>28</v>
-      </c>
-      <c r="B34" s="13" t="s">
+      <c r="B72" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="13">
         <v>67</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="B73" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="13">
         <v>68</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="B74" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="13">
         <v>69</v>
       </c>
-    </row>
-    <row r="35" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>29</v>
-      </c>
-      <c r="B35" s="13" t="s">
+      <c r="B75" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="13">
         <v>70</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
-        <v>30</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>31</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-    </row>
-    <row r="38" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
-        <v>32</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
-        <v>33</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-    </row>
-    <row r="40" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
-        <v>34</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
-        <v>35</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
-        <v>36</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
-        <v>37</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
-        <v>38</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="45" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="12">
-        <v>39</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>40</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
-        <v>41</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-    </row>
-    <row r="48" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
-        <v>42</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="12">
-        <v>43</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
-        <v>44</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
-        <v>45</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
-        <v>46</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
-        <v>47</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="54" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
-        <v>48</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="12">
-        <v>49</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="56" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
-        <v>50</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
-        <v>51</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
-        <v>52</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="12">
-        <v>53</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="60" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12">
-        <v>54</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-    </row>
-    <row r="61" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="12">
-        <v>55</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="12">
-        <v>56</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="63" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="12">
-        <v>57</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-    </row>
-    <row r="64" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="12">
-        <v>58</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="65" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="12">
-        <v>59</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="66" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="12">
-        <v>60</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="12">
-        <v>61</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
-        <v>62</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="12">
-        <v>63</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="70" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
-        <v>64</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="71" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="12">
-        <v>65</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="12">
-        <v>66</v>
-      </c>
-      <c r="B72" s="13" t="s">
+      <c r="B76" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C76" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D72" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="12">
-        <v>67</v>
-      </c>
-      <c r="B73" s="13" t="s">
+      <c r="D76" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="12">
-        <v>68</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="75" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="12">
-        <v>69</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" ht="38.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="12">
-        <v>70</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
@@ -2239,6 +2343,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>